--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-probleme.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-probleme.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9176" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9176" uniqueCount="633">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -854,6 +854,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Observation.statusCode</t>
@@ -8862,7 +8866,7 @@
         <v>74</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>74</v>
+        <v>274</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>74</v>
@@ -8870,10 +8874,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8899,10 +8903,10 @@
         <v>91</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8933,7 +8937,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -8951,7 +8955,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8971,10 +8975,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9072,10 +9076,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9116,7 +9120,7 @@
         <v>74</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>74</v>
@@ -9175,10 +9179,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9278,10 +9282,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9381,10 +9385,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9484,10 +9488,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9587,10 +9591,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9688,10 +9692,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9789,10 +9793,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9892,10 +9896,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9995,10 +9999,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10098,10 +10102,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10124,13 +10128,13 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10181,7 +10185,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -10201,10 +10205,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10227,7 +10231,7 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
@@ -10260,7 +10264,7 @@
       </c>
       <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -10278,7 +10282,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -10298,10 +10302,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10324,7 +10328,7 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
@@ -10377,7 +10381,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -10397,10 +10401,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10456,25 +10460,25 @@
       </c>
       <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -10494,10 +10498,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10523,7 +10527,7 @@
         <v>182</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
@@ -10575,7 +10579,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -10595,10 +10599,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10696,10 +10700,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10799,10 +10803,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10902,10 +10906,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11005,10 +11009,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11108,10 +11112,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11211,10 +11215,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11312,10 +11316,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11413,10 +11417,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11516,10 +11520,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11617,10 +11621,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11718,10 +11722,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11821,10 +11825,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11922,10 +11926,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12025,10 +12029,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12126,10 +12130,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12223,10 +12227,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12328,10 +12332,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12431,10 +12435,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12526,7 +12530,7 @@
         <v>74</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>74</v>
+        <v>274</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>74</v>
@@ -12534,10 +12538,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12637,10 +12641,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12740,10 +12744,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12766,7 +12770,7 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
@@ -12799,25 +12803,25 @@
       </c>
       <c r="Y103" s="2"/>
       <c r="Z103" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF103" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -12837,10 +12841,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12863,7 +12867,7 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -12896,25 +12900,25 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF104" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -12934,10 +12938,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12964,7 +12968,7 @@
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13015,7 +13019,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -13035,10 +13039,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13061,7 +13065,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -13114,7 +13118,7 @@
         <v>74</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -13134,10 +13138,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13160,7 +13164,7 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
@@ -13213,7 +13217,7 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -13233,10 +13237,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13259,7 +13263,7 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -13312,7 +13316,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -13332,10 +13336,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13358,7 +13362,7 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -13411,7 +13415,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -13431,10 +13435,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13457,7 +13461,7 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -13510,7 +13514,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -13530,10 +13534,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13556,7 +13560,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -13609,7 +13613,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13629,10 +13633,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13655,7 +13659,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13696,7 +13700,7 @@
         <v>74</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AC112" s="2"/>
       <c r="AD112" t="s" s="2">
@@ -13706,7 +13710,7 @@
         <v>125</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13726,13 +13730,13 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D113" t="s" s="2">
         <v>74</v>
@@ -13754,10 +13758,10 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
@@ -13809,7 +13813,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13829,10 +13833,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13930,10 +13934,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14031,10 +14035,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14132,10 +14136,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14233,10 +14237,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14336,10 +14340,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14439,10 +14443,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14542,10 +14546,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14645,10 +14649,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14746,10 +14750,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14786,7 +14790,7 @@
         <v>74</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>74</v>
@@ -14805,7 +14809,7 @@
       </c>
       <c r="Y123" s="2"/>
       <c r="Z123" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>74</v>
@@ -14823,7 +14827,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>75</v>
@@ -14843,10 +14847,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14873,7 +14877,7 @@
       </c>
       <c r="L124" s="2"/>
       <c r="M124" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14885,7 +14889,7 @@
         <v>74</v>
       </c>
       <c r="S124" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>74</v>
@@ -14924,7 +14928,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14944,10 +14948,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14974,12 +14978,12 @@
       </c>
       <c r="L125" s="2"/>
       <c r="M125" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
@@ -15025,7 +15029,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -15045,10 +15049,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -15124,7 +15128,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -15144,10 +15148,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15170,7 +15174,7 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" s="2"/>
@@ -15223,7 +15227,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -15243,10 +15247,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15269,7 +15273,7 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" s="2"/>
@@ -15322,7 +15326,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -15342,10 +15346,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15368,7 +15372,7 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -15421,7 +15425,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -15441,10 +15445,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15467,7 +15471,7 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -15520,7 +15524,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -15540,10 +15544,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15566,7 +15570,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -15619,7 +15623,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -15639,10 +15643,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15665,7 +15669,7 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -15718,7 +15722,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15738,10 +15742,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15764,7 +15768,7 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15817,7 +15821,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15837,10 +15841,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15863,7 +15867,7 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15916,7 +15920,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15936,10 +15940,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15962,7 +15966,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -16015,7 +16019,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -16035,10 +16039,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16061,7 +16065,7 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -16114,7 +16118,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -16134,10 +16138,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16160,7 +16164,7 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -16213,7 +16217,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -16233,13 +16237,13 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D138" t="s" s="2">
         <v>74</v>
@@ -16261,10 +16265,10 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M138" s="2"/>
       <c r="N138" s="2"/>
@@ -16316,7 +16320,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -16336,10 +16340,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16437,10 +16441,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16538,10 +16542,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16639,10 +16643,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16740,10 +16744,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16843,10 +16847,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16946,10 +16950,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17049,10 +17053,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17152,10 +17156,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17253,10 +17257,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17293,7 +17297,7 @@
         <v>74</v>
       </c>
       <c r="S148" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="T148" t="s" s="2">
         <v>74</v>
@@ -17312,7 +17316,7 @@
       </c>
       <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>74</v>
@@ -17330,7 +17334,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>75</v>
@@ -17350,10 +17354,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17380,7 +17384,7 @@
       </c>
       <c r="L149" s="2"/>
       <c r="M149" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -17431,7 +17435,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -17451,10 +17455,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17481,12 +17485,12 @@
       </c>
       <c r="L150" s="2"/>
       <c r="M150" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q150" s="2"/>
       <c r="R150" t="s" s="2">
@@ -17532,7 +17536,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -17552,10 +17556,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17631,7 +17635,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -17651,10 +17655,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17677,7 +17681,7 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" s="2"/>
@@ -17730,7 +17734,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17750,10 +17754,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17776,7 +17780,7 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" s="2"/>
@@ -17829,7 +17833,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17849,10 +17853,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17875,7 +17879,7 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17928,7 +17932,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17948,10 +17952,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17974,7 +17978,7 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -18027,7 +18031,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -18047,10 +18051,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18073,7 +18077,7 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -18126,7 +18130,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -18146,10 +18150,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18172,7 +18176,7 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -18225,7 +18229,7 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
@@ -18245,10 +18249,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18271,7 +18275,7 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -18324,7 +18328,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -18344,10 +18348,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18370,7 +18374,7 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -18423,7 +18427,7 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
@@ -18443,10 +18447,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18469,7 +18473,7 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
@@ -18522,7 +18526,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -18542,10 +18546,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18568,7 +18572,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18621,7 +18625,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18641,10 +18645,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18667,7 +18671,7 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18720,7 +18724,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18740,13 +18744,13 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D163" t="s" s="2">
         <v>74</v>
@@ -18768,10 +18772,10 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M163" s="2"/>
       <c r="N163" s="2"/>
@@ -18823,7 +18827,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18843,10 +18847,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18944,10 +18948,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -19045,10 +19049,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19146,10 +19150,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19247,10 +19251,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19350,10 +19354,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19453,10 +19457,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19556,10 +19560,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19659,10 +19663,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19760,10 +19764,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19800,7 +19804,7 @@
         <v>74</v>
       </c>
       <c r="S173" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="T173" t="s" s="2">
         <v>74</v>
@@ -19819,7 +19823,7 @@
       </c>
       <c r="Y173" s="2"/>
       <c r="Z173" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>74</v>
@@ -19837,7 +19841,7 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>75</v>
@@ -19857,10 +19861,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19887,7 +19891,7 @@
       </c>
       <c r="L174" s="2"/>
       <c r="M174" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -19938,7 +19942,7 @@
         <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -19958,10 +19962,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19988,12 +19992,12 @@
       </c>
       <c r="L175" s="2"/>
       <c r="M175" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
@@ -20039,7 +20043,7 @@
         <v>74</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -20059,10 +20063,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20138,7 +20142,7 @@
         <v>74</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -20158,10 +20162,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20184,7 +20188,7 @@
         <v>74</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
@@ -20237,7 +20241,7 @@
         <v>74</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -20257,10 +20261,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20283,7 +20287,7 @@
         <v>74</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
@@ -20336,7 +20340,7 @@
         <v>74</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
@@ -20356,10 +20360,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20382,7 +20386,7 @@
         <v>74</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
@@ -20435,7 +20439,7 @@
         <v>74</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>80</v>
@@ -20455,10 +20459,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20481,7 +20485,7 @@
         <v>74</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
@@ -20534,7 +20538,7 @@
         <v>74</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>80</v>
@@ -20554,10 +20558,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20580,7 +20584,7 @@
         <v>74</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L181" s="2"/>
       <c r="M181" s="2"/>
@@ -20633,7 +20637,7 @@
         <v>74</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -20653,10 +20657,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20679,7 +20683,7 @@
         <v>74</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
@@ -20732,7 +20736,7 @@
         <v>74</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>80</v>
@@ -20752,10 +20756,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20778,7 +20782,7 @@
         <v>74</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
@@ -20831,7 +20835,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -20851,10 +20855,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20877,7 +20881,7 @@
         <v>74</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
@@ -20930,7 +20934,7 @@
         <v>74</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>80</v>
@@ -20950,10 +20954,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20976,7 +20980,7 @@
         <v>74</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
@@ -21029,7 +21033,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -21049,10 +21053,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21075,7 +21079,7 @@
         <v>74</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
@@ -21128,7 +21132,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -21148,10 +21152,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21174,7 +21178,7 @@
         <v>74</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
@@ -21227,7 +21231,7 @@
         <v>74</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -21247,13 +21251,13 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D188" t="s" s="2">
         <v>74</v>
@@ -21275,10 +21279,10 @@
         <v>74</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M188" s="2"/>
       <c r="N188" s="2"/>
@@ -21330,7 +21334,7 @@
         <v>74</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -21350,10 +21354,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21451,10 +21455,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21552,10 +21556,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21653,10 +21657,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21754,10 +21758,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21857,10 +21861,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21960,10 +21964,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -22063,10 +22067,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22166,10 +22170,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22267,10 +22271,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22307,7 +22311,7 @@
         <v>74</v>
       </c>
       <c r="S198" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="T198" t="s" s="2">
         <v>74</v>
@@ -22326,7 +22330,7 @@
       </c>
       <c r="Y198" s="2"/>
       <c r="Z198" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>74</v>
@@ -22344,7 +22348,7 @@
         <v>74</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>75</v>
@@ -22364,10 +22368,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22394,7 +22398,7 @@
       </c>
       <c r="L199" s="2"/>
       <c r="M199" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -22406,7 +22410,7 @@
         <v>74</v>
       </c>
       <c r="S199" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T199" t="s" s="2">
         <v>74</v>
@@ -22445,7 +22449,7 @@
         <v>74</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -22465,10 +22469,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22495,12 +22499,12 @@
       </c>
       <c r="L200" s="2"/>
       <c r="M200" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q200" s="2"/>
       <c r="R200" t="s" s="2">
@@ -22546,7 +22550,7 @@
         <v>74</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -22566,10 +22570,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22645,7 +22649,7 @@
         <v>74</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -22665,10 +22669,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22691,7 +22695,7 @@
         <v>74</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" s="2"/>
@@ -22744,7 +22748,7 @@
         <v>74</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -22764,10 +22768,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22790,7 +22794,7 @@
         <v>74</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" s="2"/>
@@ -22843,7 +22847,7 @@
         <v>74</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
@@ -22863,10 +22867,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22889,7 +22893,7 @@
         <v>74</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
@@ -22942,7 +22946,7 @@
         <v>74</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>80</v>
@@ -22962,10 +22966,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22988,7 +22992,7 @@
         <v>74</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
@@ -23041,7 +23045,7 @@
         <v>74</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>80</v>
@@ -23061,10 +23065,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -23087,7 +23091,7 @@
         <v>74</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L206" s="2"/>
       <c r="M206" s="2"/>
@@ -23140,7 +23144,7 @@
         <v>74</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
@@ -23160,10 +23164,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23186,7 +23190,7 @@
         <v>74</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L207" s="2"/>
       <c r="M207" s="2"/>
@@ -23239,7 +23243,7 @@
         <v>74</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>80</v>
@@ -23259,10 +23263,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23285,7 +23289,7 @@
         <v>74</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L208" s="2"/>
       <c r="M208" s="2"/>
@@ -23338,7 +23342,7 @@
         <v>74</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -23358,10 +23362,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23384,7 +23388,7 @@
         <v>74</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L209" s="2"/>
       <c r="M209" s="2"/>
@@ -23437,7 +23441,7 @@
         <v>74</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>80</v>
@@ -23457,10 +23461,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23483,7 +23487,7 @@
         <v>74</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
@@ -23536,7 +23540,7 @@
         <v>74</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -23556,10 +23560,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23582,7 +23586,7 @@
         <v>74</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
@@ -23635,7 +23639,7 @@
         <v>74</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -23655,10 +23659,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23681,7 +23685,7 @@
         <v>74</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
@@ -23734,7 +23738,7 @@
         <v>74</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -23754,13 +23758,13 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D213" t="s" s="2">
         <v>74</v>
@@ -23782,10 +23786,10 @@
         <v>74</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M213" s="2"/>
       <c r="N213" s="2"/>
@@ -23837,7 +23841,7 @@
         <v>74</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -23857,10 +23861,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23958,10 +23962,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -24059,10 +24063,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24160,10 +24164,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24261,10 +24265,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24364,10 +24368,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24467,10 +24471,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24570,10 +24574,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24673,10 +24677,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24774,10 +24778,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24814,7 +24818,7 @@
         <v>74</v>
       </c>
       <c r="S223" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="T223" t="s" s="2">
         <v>74</v>
@@ -24833,7 +24837,7 @@
       </c>
       <c r="Y223" s="2"/>
       <c r="Z223" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>74</v>
@@ -24851,7 +24855,7 @@
         <v>74</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>75</v>
@@ -24871,10 +24875,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24901,7 +24905,7 @@
       </c>
       <c r="L224" s="2"/>
       <c r="M224" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -24913,7 +24917,7 @@
         <v>74</v>
       </c>
       <c r="S224" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T224" t="s" s="2">
         <v>74</v>
@@ -24952,7 +24956,7 @@
         <v>74</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -24972,10 +24976,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -25002,12 +25006,12 @@
       </c>
       <c r="L225" s="2"/>
       <c r="M225" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q225" s="2"/>
       <c r="R225" t="s" s="2">
@@ -25053,7 +25057,7 @@
         <v>74</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -25073,10 +25077,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -25152,7 +25156,7 @@
         <v>74</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>80</v>
@@ -25172,10 +25176,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25198,7 +25202,7 @@
         <v>74</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L227" s="2"/>
       <c r="M227" s="2"/>
@@ -25251,7 +25255,7 @@
         <v>74</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>80</v>
@@ -25271,10 +25275,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25297,7 +25301,7 @@
         <v>74</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L228" s="2"/>
       <c r="M228" s="2"/>
@@ -25350,7 +25354,7 @@
         <v>74</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>80</v>
@@ -25370,10 +25374,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25396,7 +25400,7 @@
         <v>74</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
@@ -25449,7 +25453,7 @@
         <v>74</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>80</v>
@@ -25469,10 +25473,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -25495,7 +25499,7 @@
         <v>74</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L230" s="2"/>
       <c r="M230" s="2"/>
@@ -25548,7 +25552,7 @@
         <v>74</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>80</v>
@@ -25568,10 +25572,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25594,7 +25598,7 @@
         <v>74</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L231" s="2"/>
       <c r="M231" s="2"/>
@@ -25647,7 +25651,7 @@
         <v>74</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>80</v>
@@ -25667,10 +25671,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25693,7 +25697,7 @@
         <v>74</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L232" s="2"/>
       <c r="M232" s="2"/>
@@ -25746,7 +25750,7 @@
         <v>74</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>80</v>
@@ -25766,10 +25770,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -25792,7 +25796,7 @@
         <v>74</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L233" s="2"/>
       <c r="M233" s="2"/>
@@ -25845,7 +25849,7 @@
         <v>74</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>80</v>
@@ -25865,10 +25869,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -25891,7 +25895,7 @@
         <v>74</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
@@ -25944,7 +25948,7 @@
         <v>74</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>80</v>
@@ -25964,10 +25968,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -25990,7 +25994,7 @@
         <v>74</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L235" s="2"/>
       <c r="M235" s="2"/>
@@ -26043,7 +26047,7 @@
         <v>74</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>80</v>
@@ -26063,10 +26067,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -26089,7 +26093,7 @@
         <v>74</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L236" s="2"/>
       <c r="M236" s="2"/>
@@ -26142,7 +26146,7 @@
         <v>74</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>80</v>
@@ -26162,10 +26166,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26188,7 +26192,7 @@
         <v>74</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L237" s="2"/>
       <c r="M237" s="2"/>
@@ -26241,7 +26245,7 @@
         <v>74</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>80</v>
@@ -26261,10 +26265,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26287,10 +26291,10 @@
         <v>74</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M238" s="2"/>
       <c r="N238" s="2"/>
@@ -26342,7 +26346,7 @@
         <v>74</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>80</v>
@@ -26362,10 +26366,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26463,10 +26467,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26564,10 +26568,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -26665,10 +26669,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -26766,10 +26770,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -26869,10 +26873,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -26972,10 +26976,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -27075,10 +27079,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -27178,10 +27182,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -27279,10 +27283,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -27319,7 +27323,7 @@
         <v>74</v>
       </c>
       <c r="S248" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="T248" t="s" s="2">
         <v>74</v>
@@ -27338,7 +27342,7 @@
       </c>
       <c r="Y248" s="2"/>
       <c r="Z248" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AA248" t="s" s="2">
         <v>74</v>
@@ -27356,7 +27360,7 @@
         <v>74</v>
       </c>
       <c r="AF248" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG248" t="s" s="2">
         <v>75</v>
@@ -27376,10 +27380,10 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
@@ -27402,7 +27406,7 @@
         <v>74</v>
       </c>
       <c r="K249" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L249" s="2"/>
       <c r="M249" s="2"/>
@@ -27455,7 +27459,7 @@
         <v>74</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>80</v>
@@ -27475,10 +27479,10 @@
     </row>
     <row r="250" hidden="true">
       <c r="A250" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -27501,7 +27505,7 @@
         <v>74</v>
       </c>
       <c r="K250" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L250" s="2"/>
       <c r="M250" s="2"/>
@@ -27554,7 +27558,7 @@
         <v>74</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>80</v>
@@ -27574,10 +27578,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -27600,7 +27604,7 @@
         <v>74</v>
       </c>
       <c r="K251" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L251" s="2"/>
       <c r="M251" s="2"/>
@@ -27653,7 +27657,7 @@
         <v>74</v>
       </c>
       <c r="AF251" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG251" t="s" s="2">
         <v>80</v>
@@ -27673,10 +27677,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -27699,7 +27703,7 @@
         <v>74</v>
       </c>
       <c r="K252" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L252" s="2"/>
       <c r="M252" s="2"/>
@@ -27752,7 +27756,7 @@
         <v>74</v>
       </c>
       <c r="AF252" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG252" t="s" s="2">
         <v>80</v>
@@ -27772,10 +27776,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -27798,7 +27802,7 @@
         <v>74</v>
       </c>
       <c r="K253" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="L253" s="2"/>
       <c r="M253" s="2"/>
@@ -27851,7 +27855,7 @@
         <v>74</v>
       </c>
       <c r="AF253" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG253" t="s" s="2">
         <v>80</v>
@@ -27871,10 +27875,10 @@
     </row>
     <row r="254" hidden="true">
       <c r="A254" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C254" s="2"/>
       <c r="D254" t="s" s="2">
@@ -27972,10 +27976,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -28073,10 +28077,10 @@
     </row>
     <row r="256" hidden="true">
       <c r="A256" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -28174,10 +28178,10 @@
     </row>
     <row r="257" hidden="true">
       <c r="A257" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -28275,10 +28279,10 @@
     </row>
     <row r="258" hidden="true">
       <c r="A258" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C258" s="2"/>
       <c r="D258" t="s" s="2">
@@ -28378,10 +28382,10 @@
     </row>
     <row r="259" hidden="true">
       <c r="A259" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C259" s="2"/>
       <c r="D259" t="s" s="2">
@@ -28481,10 +28485,10 @@
     </row>
     <row r="260" hidden="true">
       <c r="A260" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C260" s="2"/>
       <c r="D260" t="s" s="2">
@@ -28584,10 +28588,10 @@
     </row>
     <row r="261" hidden="true">
       <c r="A261" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C261" s="2"/>
       <c r="D261" t="s" s="2">
@@ -28687,10 +28691,10 @@
     </row>
     <row r="262" hidden="true">
       <c r="A262" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C262" s="2"/>
       <c r="D262" t="s" s="2">
@@ -28788,10 +28792,10 @@
     </row>
     <row r="263" hidden="true">
       <c r="A263" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C263" s="2"/>
       <c r="D263" t="s" s="2">
@@ -28821,14 +28825,14 @@
       <c r="N263" s="2"/>
       <c r="O263" s="2"/>
       <c r="P263" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Q263" s="2"/>
       <c r="R263" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S263" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="T263" t="s" s="2">
         <v>74</v>
@@ -28847,7 +28851,7 @@
       </c>
       <c r="Y263" s="2"/>
       <c r="Z263" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA263" t="s" s="2">
         <v>74</v>
@@ -28865,7 +28869,7 @@
         <v>74</v>
       </c>
       <c r="AF263" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG263" t="s" s="2">
         <v>80</v>
@@ -28885,10 +28889,10 @@
     </row>
     <row r="264" hidden="true">
       <c r="A264" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C264" s="2"/>
       <c r="D264" t="s" s="2">
@@ -28944,7 +28948,7 @@
       </c>
       <c r="Y264" s="2"/>
       <c r="Z264" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA264" t="s" s="2">
         <v>74</v>
@@ -28962,7 +28966,7 @@
         <v>74</v>
       </c>
       <c r="AF264" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG264" t="s" s="2">
         <v>80</v>
@@ -28982,10 +28986,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C265" s="2"/>
       <c r="D265" t="s" s="2">
@@ -29011,7 +29015,7 @@
         <v>95</v>
       </c>
       <c r="L265" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M265" s="2"/>
       <c r="N265" s="2"/>
@@ -29063,7 +29067,7 @@
         <v>74</v>
       </c>
       <c r="AF265" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG265" t="s" s="2">
         <v>80</v>
@@ -29083,10 +29087,10 @@
     </row>
     <row r="266" hidden="true">
       <c r="A266" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C266" s="2"/>
       <c r="D266" t="s" s="2">
@@ -29142,7 +29146,7 @@
       </c>
       <c r="Y266" s="2"/>
       <c r="Z266" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AA266" t="s" s="2">
         <v>74</v>
@@ -29160,7 +29164,7 @@
         <v>74</v>
       </c>
       <c r="AF266" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG266" t="s" s="2">
         <v>80</v>
@@ -29180,10 +29184,10 @@
     </row>
     <row r="267" hidden="true">
       <c r="A267" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C267" s="2"/>
       <c r="D267" t="s" s="2">
@@ -29259,7 +29263,7 @@
         <v>74</v>
       </c>
       <c r="AF267" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG267" t="s" s="2">
         <v>80</v>
@@ -29279,10 +29283,10 @@
     </row>
     <row r="268" hidden="true">
       <c r="A268" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C268" s="2"/>
       <c r="D268" t="s" s="2">
@@ -29380,10 +29384,10 @@
     </row>
     <row r="269" hidden="true">
       <c r="A269" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C269" s="2"/>
       <c r="D269" t="s" s="2">
@@ -29481,10 +29485,10 @@
     </row>
     <row r="270" hidden="true">
       <c r="A270" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C270" s="2"/>
       <c r="D270" t="s" s="2">
@@ -29584,10 +29588,10 @@
     </row>
     <row r="271" hidden="true">
       <c r="A271" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C271" s="2"/>
       <c r="D271" t="s" s="2">
@@ -29685,10 +29689,10 @@
     </row>
     <row r="272" hidden="true">
       <c r="A272" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" t="s" s="2">
@@ -29788,10 +29792,10 @@
     </row>
     <row r="273" hidden="true">
       <c r="A273" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" t="s" s="2">
@@ -29889,10 +29893,10 @@
     </row>
     <row r="274" hidden="true">
       <c r="A274" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" t="s" s="2">
@@ -29986,10 +29990,10 @@
     </row>
     <row r="275" hidden="true">
       <c r="A275" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" t="s" s="2">
@@ -30091,10 +30095,10 @@
     </row>
     <row r="276" hidden="true">
       <c r="A276" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" t="s" s="2">
@@ -30122,7 +30126,7 @@
         <v>267</v>
       </c>
       <c r="L276" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M276" t="s" s="2">
         <v>268</v>
@@ -30196,10 +30200,10 @@
     </row>
     <row r="277" hidden="true">
       <c r="A277" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" t="s" s="2">
@@ -30291,7 +30295,7 @@
         <v>74</v>
       </c>
       <c r="AJ277" t="s" s="2">
-        <v>74</v>
+        <v>274</v>
       </c>
       <c r="AK277" t="s" s="2">
         <v>74</v>
@@ -30299,10 +30303,10 @@
     </row>
     <row r="278" hidden="true">
       <c r="A278" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C278" s="2"/>
       <c r="D278" t="s" s="2">
@@ -30378,7 +30382,7 @@
         <v>74</v>
       </c>
       <c r="AF278" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG278" t="s" s="2">
         <v>80</v>
@@ -30398,10 +30402,10 @@
     </row>
     <row r="279" hidden="true">
       <c r="A279" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C279" s="2"/>
       <c r="D279" t="s" s="2">
@@ -30424,7 +30428,7 @@
         <v>74</v>
       </c>
       <c r="K279" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L279" s="2"/>
       <c r="M279" s="2"/>
@@ -30477,7 +30481,7 @@
         <v>74</v>
       </c>
       <c r="AF279" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AG279" t="s" s="2">
         <v>80</v>
@@ -30497,10 +30501,10 @@
     </row>
     <row r="280" hidden="true">
       <c r="A280" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" t="s" s="2">
@@ -30523,7 +30527,7 @@
         <v>74</v>
       </c>
       <c r="K280" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="L280" s="2"/>
       <c r="M280" s="2"/>
@@ -30576,7 +30580,7 @@
         <v>74</v>
       </c>
       <c r="AF280" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG280" t="s" s="2">
         <v>80</v>
@@ -30596,10 +30600,10 @@
     </row>
     <row r="281" hidden="true">
       <c r="A281" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" t="s" s="2">
@@ -30622,7 +30626,7 @@
         <v>74</v>
       </c>
       <c r="K281" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L281" s="2"/>
       <c r="M281" s="2"/>
@@ -30675,7 +30679,7 @@
         <v>74</v>
       </c>
       <c r="AF281" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG281" t="s" s="2">
         <v>80</v>
@@ -30695,10 +30699,10 @@
     </row>
     <row r="282" hidden="true">
       <c r="A282" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" t="s" s="2">
@@ -30721,7 +30725,7 @@
         <v>74</v>
       </c>
       <c r="K282" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L282" s="2"/>
       <c r="M282" s="2"/>
@@ -30774,7 +30778,7 @@
         <v>74</v>
       </c>
       <c r="AF282" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG282" t="s" s="2">
         <v>80</v>
@@ -30794,10 +30798,10 @@
     </row>
     <row r="283" hidden="true">
       <c r="A283" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" t="s" s="2">
@@ -30820,11 +30824,11 @@
         <v>74</v>
       </c>
       <c r="K283" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="L283" s="2"/>
       <c r="M283" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N283" s="2"/>
       <c r="O283" s="2"/>
@@ -30875,7 +30879,7 @@
         <v>74</v>
       </c>
       <c r="AF283" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG283" t="s" s="2">
         <v>80</v>
@@ -30895,10 +30899,10 @@
     </row>
     <row r="284" hidden="true">
       <c r="A284" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" t="s" s="2">
@@ -30996,10 +31000,10 @@
     </row>
     <row r="285" hidden="true">
       <c r="A285" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" t="s" s="2">
@@ -31097,10 +31101,10 @@
     </row>
     <row r="286" hidden="true">
       <c r="A286" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" t="s" s="2">
@@ -31198,10 +31202,10 @@
     </row>
     <row r="287" hidden="true">
       <c r="A287" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C287" s="2"/>
       <c r="D287" t="s" s="2">
@@ -31299,10 +31303,10 @@
     </row>
     <row r="288" hidden="true">
       <c r="A288" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C288" s="2"/>
       <c r="D288" t="s" s="2">
@@ -31402,10 +31406,10 @@
     </row>
     <row r="289" hidden="true">
       <c r="A289" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C289" s="2"/>
       <c r="D289" t="s" s="2">
@@ -31505,10 +31509,10 @@
     </row>
     <row r="290" hidden="true">
       <c r="A290" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C290" s="2"/>
       <c r="D290" t="s" s="2">
@@ -31608,10 +31612,10 @@
     </row>
     <row r="291" hidden="true">
       <c r="A291" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C291" s="2"/>
       <c r="D291" t="s" s="2">
@@ -31711,10 +31715,10 @@
     </row>
     <row r="292" hidden="true">
       <c r="A292" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C292" s="2"/>
       <c r="D292" t="s" s="2">
@@ -31812,10 +31816,10 @@
     </row>
     <row r="293" hidden="true">
       <c r="A293" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C293" s="2"/>
       <c r="D293" t="s" s="2">
@@ -31849,7 +31853,7 @@
       </c>
       <c r="Q293" s="2"/>
       <c r="R293" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="S293" t="s" s="2">
         <v>74</v>
@@ -31871,7 +31875,7 @@
       </c>
       <c r="Y293" s="2"/>
       <c r="Z293" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AA293" t="s" s="2">
         <v>74</v>
@@ -31889,7 +31893,7 @@
         <v>74</v>
       </c>
       <c r="AF293" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG293" t="s" s="2">
         <v>80</v>
@@ -31909,10 +31913,10 @@
     </row>
     <row r="294" hidden="true">
       <c r="A294" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C294" s="2"/>
       <c r="D294" t="s" s="2">
@@ -31935,7 +31939,7 @@
         <v>74</v>
       </c>
       <c r="K294" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L294" s="2"/>
       <c r="M294" s="2"/>
@@ -31988,7 +31992,7 @@
         <v>74</v>
       </c>
       <c r="AF294" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="AG294" t="s" s="2">
         <v>75</v>
@@ -32008,10 +32012,10 @@
     </row>
     <row r="295" hidden="true">
       <c r="A295" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C295" s="2"/>
       <c r="D295" t="s" s="2">
@@ -32034,7 +32038,7 @@
         <v>74</v>
       </c>
       <c r="K295" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L295" s="2"/>
       <c r="M295" s="2"/>
@@ -32087,7 +32091,7 @@
         <v>74</v>
       </c>
       <c r="AF295" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG295" t="s" s="2">
         <v>80</v>
